--- a/results/consolidated/Methodology_Consolidated.xlsx
+++ b/results/consolidated/Methodology_Consolidated.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t xml:space="preserve">Section</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t xml:space="preserve">gjrGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sGARCH</t>
   </si>
   <si>
     <t xml:space="preserve">sGARCH_norm</t>
@@ -1052,31 +1049,31 @@
         <v>72</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08</v>
+        <v>0.085</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0315</v>
+        <v>0.7023</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112</v>
+        <v>0.5849</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1084,31 +1081,31 @@
         <v>73</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0.01</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0836</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4416</v>
+        <v>0.5652</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7983</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1116,28 +1113,28 @@
         <v>74</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0951</v>
+        <v>0.0899</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0579</v>
+        <v>0.5285</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1425</v>
+        <v>0.5372</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -1157,22 +1154,22 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.0884</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1239</v>
+        <v>0.5719</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.141</v>
+        <v>0.1555</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1180,63 +1177,31 @@
         <v>76</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0749</v>
+        <v>0.0893</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0289</v>
+        <v>0.6636</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0213</v>
+        <v>0.3336</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0249</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0519</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1252,72 +1217,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>83</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
         <v>86</v>
-      </c>
-      <c r="B3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
         <v>88</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>89</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
         <v>92</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>93</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1339,22 +1304,22 @@
         <v>63</v>
       </c>
       <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
         <v>96</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>97</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>98</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>100</v>
-      </c>
-      <c r="H1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2">
@@ -1362,25 +1327,25 @@
         <v>72</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4304</v>
+        <v>0.4795</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1792</v>
+        <v>0.1963</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9996</v>
+        <v>1.0412</v>
       </c>
     </row>
     <row r="3">
@@ -1388,23 +1353,25 @@
         <v>73</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C3"/>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0716</v>
+      </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3154</v>
+        <v>0.4443</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3952</v>
+        <v>0.6773</v>
       </c>
     </row>
     <row r="4">
@@ -1412,25 +1379,25 @@
         <v>74</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3689</v>
+        <v>0.3584</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1997</v>
+        <v>0.1695</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9855</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="5">
@@ -1441,7 +1408,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3328</v>
+        <v>0.3104</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -1450,13 +1417,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1543</v>
+        <v>0.1504</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9958</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="6">
@@ -1464,51 +1431,25 @@
         <v>76</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2912</v>
+        <v>0.3655</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1368</v>
+        <v>0.165</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.012</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3086</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.0094</v>
+        <v>0.9403</v>
       </c>
     </row>
   </sheetData>
@@ -1524,57 +1465,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>103</v>
-      </c>
-      <c r="C1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="s">
         <v>105</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>106</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
         <v>108</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>109</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
         <v>111</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>112</v>
-      </c>
-      <c r="C4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
         <v>114</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>115</v>
-      </c>
-      <c r="C5" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
